--- a/java/spring/spring_boot.xlsx
+++ b/java/spring/spring_boot.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21648" windowHeight="9155" firstSheet="61" activeTab="64"/>
+    <workbookView windowWidth="22368" windowHeight="9564" firstSheet="61" activeTab="64"/>
   </bookViews>
   <sheets>
     <sheet name="org.springframework.boot" sheetId="1" r:id="rId1"/>
@@ -1941,7 +1941,7 @@
     <col min="1" max="1" width="22.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" ht="25.2" spans="1:1">
+    <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
         <v>22</v>
       </c>
@@ -2165,7 +2165,7 @@
     <col min="1" max="1" width="48.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" ht="25.2" spans="1:1">
+    <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
         <v>74</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" ht="25.2" spans="1:1">
+    <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -2290,7 +2290,7 @@
     <col min="1" max="1" width="41.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" ht="25.2" spans="1:1">
+    <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
         <v>74</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" ht="25.2" spans="1:1">
+    <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" ht="25.2" spans="1:1">
+    <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
         <v>74</v>
       </c>
@@ -2619,7 +2619,7 @@
     <col min="1" max="1" width="99.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="11" ht="25.2" spans="1:1">
+    <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -2816,7 +2816,7 @@
     <col min="1" max="1" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2891,7 +2891,7 @@
     <col min="1" max="1" width="40.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2968,7 +2968,7 @@
     <col min="1" max="1" width="41.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="14" ht="25.2" spans="1:1">
+    <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
         <v>74</v>
       </c>
@@ -3221,7 +3221,7 @@
     <col min="1" max="1" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="7" ht="25.2" spans="1:1">
+    <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
@@ -3414,7 +3414,7 @@
     <col min="1" max="16384" width="37.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="13" ht="25.2" spans="1:1">
+    <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
         <v>74</v>
       </c>
@@ -3633,7 +3633,7 @@
     <col min="1" max="1" width="29.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3948,7 +3948,7 @@
     <col min="1" max="1" width="45.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="31" ht="25.2" spans="1:1">
+    <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
         <v>74</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="36" ht="25.2" spans="1:1">
+    <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
         <v>22</v>
       </c>
@@ -4108,7 +4108,7 @@
     <col min="1" max="1" width="55.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="22" ht="25.2" spans="1:1">
+    <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
         <v>22</v>
       </c>
@@ -4327,7 +4327,7 @@
     <col min="1" max="1" width="36.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4382,7 +4382,7 @@
     <col min="1" max="1" width="40.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4546,7 +4546,7 @@
     <col min="1" max="16384" width="85.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>

--- a/java/spring/spring_boot.xlsx
+++ b/java/spring/spring_boot.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9564" firstSheet="61" activeTab="64"/>
+    <workbookView windowWidth="22368" windowHeight="9564" firstSheet="61" activeTab="61"/>
   </bookViews>
   <sheets>
     <sheet name="org.springframework.boot" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="334">
   <si>
     <r>
       <rPr>
@@ -770,6 +770,186 @@
     </r>
   </si>
   <si>
+    <t>RestTemplateCustomizer</t>
+  </si>
+  <si>
+    <t>RestTemplateRequestCustomizer</t>
+  </si>
+  <si>
+    <t>ClientHttpRequestFactorySupplier</t>
+  </si>
+  <si>
+    <t>RestTemplateBuilder</t>
+  </si>
+  <si>
+    <t>RootUriTemplateHandler</t>
+  </si>
+  <si>
+    <t>CodecCustomizer</t>
+  </si>
+  <si>
+    <t>ConfigurableWebServerApplicationContext</t>
+  </si>
+  <si>
+    <t>WebServerApplicationContext</t>
+  </si>
+  <si>
+    <t>ServerPortInfoApplicationContextInitializer</t>
+  </si>
+  <si>
+    <t>WebServerInitializedEvent</t>
+  </si>
+  <si>
+    <t>WebServerPortFileWriter</t>
+  </si>
+  <si>
+    <t>ConfigurableJettyWebServerFactory</t>
+  </si>
+  <si>
+    <t>JettyServerCustomizer</t>
+  </si>
+  <si>
+    <t>JettyReactiveWebServerFactory</t>
+  </si>
+  <si>
+    <t>JettyServletWebServerFactory</t>
+  </si>
+  <si>
+    <t>JettyWebServer</t>
+  </si>
+  <si>
+    <t>ServletContextInitializerConfiguration</t>
+  </si>
+  <si>
+    <t>NettyRouteProvider</t>
+  </si>
+  <si>
+    <t>NettyServerCustomizer</t>
+  </si>
+  <si>
+    <t>NettyReactiveWebServerFactory</t>
+  </si>
+  <si>
+    <t>NettyWebServer</t>
+  </si>
+  <si>
+    <t>SslServerCustomizer</t>
+  </si>
+  <si>
+    <t>ConfigurableTomcatWebServerFactory</t>
+  </si>
+  <si>
+    <t>TomcatConnectorCustomizer</t>
+  </si>
+  <si>
+    <t>TomcatContextCustomizer</t>
+  </si>
+  <si>
+    <t>TomcatProtocolHandlerCustomizer</t>
+  </si>
+  <si>
+    <t>TomcatEmbeddedWebappClassLoader</t>
+  </si>
+  <si>
+    <t>TomcatReactiveWebServerFactory</t>
+  </si>
+  <si>
+    <t>TomcatServletWebServerFactory</t>
+  </si>
+  <si>
+    <t>TomcatWebServer</t>
+  </si>
+  <si>
+    <t>ConnectorStartFailedException</t>
+  </si>
+  <si>
+    <t>ConfigurableUndertowWebServerFactory</t>
+  </si>
+  <si>
+    <t>HttpHandlerFactory</t>
+  </si>
+  <si>
+    <t>UndertowBuilderCustomizer</t>
+  </si>
+  <si>
+    <t>UndertowDeploymentInfoCustomizer</t>
+  </si>
+  <si>
+    <t>UndertowReactiveWebServerFactory</t>
+  </si>
+  <si>
+    <t>UndertowServletWebServer</t>
+  </si>
+  <si>
+    <t>UndertowServletWebServerFactory</t>
+  </si>
+  <si>
+    <t>UndertowWebServer</t>
+  </si>
+  <si>
+    <t>ErrorAttributes</t>
+  </si>
+  <si>
+    <t>ErrorWebExceptionHandler</t>
+  </si>
+  <si>
+    <t>DefaultErrorAttributes</t>
+  </si>
+  <si>
+    <t>ConfigurableReactiveWebApplicationContext</t>
+  </si>
+  <si>
+    <t>ConfigurableReactiveWebEnvironment</t>
+  </si>
+  <si>
+    <t>ReactiveWebApplicationContext</t>
+  </si>
+  <si>
+    <t>AnnotationConfigReactiveWebApplicationContext</t>
+  </si>
+  <si>
+    <t>AnnotationConfigReactiveWebServerApplicationContext</t>
+  </si>
+  <si>
+    <t>GenericReactiveWebApplicationContext</t>
+  </si>
+  <si>
+    <t>ReactiveWebServerApplicationContext</t>
+  </si>
+  <si>
+    <t>ReactiveWebServerInitializedEvent</t>
+  </si>
+  <si>
+    <t>StandardReactiveWebEnvironment</t>
+  </si>
+  <si>
+    <t>org.springframework.boot.web.reactive.filter</t>
+  </si>
+  <si>
+    <t>OrderedWebFilter</t>
+  </si>
+  <si>
+    <t>OrderedHiddenHttpMethodFilter</t>
+  </si>
+  <si>
+    <t>WebClientCustomizer</t>
+  </si>
+  <si>
+    <t>MustacheView</t>
+  </si>
+  <si>
+    <t>MustacheViewResolver</t>
+  </si>
+  <si>
+    <t>ConfigurableReactiveWebServerFactory</t>
+  </si>
+  <si>
+    <t>ReactiveWebServerFactory</t>
+  </si>
+  <si>
+    <t>AbstractReactiveWebServerFactory</t>
+  </si>
+  <si>
     <t>ConfigurableWebServerFactory</t>
   </si>
   <si>
@@ -902,15 +1082,9 @@
     <t>XmlServletWebServerApplicationContext</t>
   </si>
   <si>
-    <t>ErrorAttributes</t>
-  </si>
-  <si>
     <t>ErrorController</t>
   </si>
   <si>
-    <t>DefaultErrorAttributes</t>
-  </si>
-  <si>
     <t>OrderedFilter</t>
   </si>
   <si>
@@ -923,9 +1097,6 @@
     <t>OrderedFormContentFilter</t>
   </si>
   <si>
-    <t>OrderedHiddenHttpMethodFilter</t>
-  </si>
-  <si>
     <t>OrderedRequestContextFilter</t>
   </si>
   <si>
@@ -963,12 +1134,6 @@
   </si>
   <si>
     <t>SpringBootServletInitializer</t>
-  </si>
-  <si>
-    <t>MustacheView</t>
-  </si>
-  <si>
-    <t>MustacheViewResolver</t>
   </si>
 </sst>
 </file>
@@ -981,7 +1146,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -997,15 +1162,29 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Courier New"/>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF4A6782"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF4A6782"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8.25"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Courier New"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1461,10 +1640,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1473,37 +1652,31 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1512,105 +1685,123 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1938,7 +2129,7 @@
   <dimension ref="A1:A31"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="22.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="46.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3367,7 +3558,7 @@
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="3"/>
+      <c r="A4" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3735,77 +3926,352 @@
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" ht="78" spans="1:1">
+      <c r="A1" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="64.3333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2"/>
+  <cols>
+    <col min="1" max="1" width="29" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="CodecCustomizer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/codec/CodecCustomizer.html"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
+  <cols>
+    <col min="1" max="1" width="36.3333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="ConfigurableWebServerApplicationContext" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/context/ConfigurableWebServerApplicationContext.html"/>
+    <hyperlink ref="A4" r:id="rId2" display="WebServerApplicationContext" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/context/WebServerApplicationContext.html"/>
+    <hyperlink ref="A8" r:id="rId3" display="ServerPortInfoApplicationContextInitializer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/context/ServerPortInfoApplicationContextInitializer.html"/>
+    <hyperlink ref="A9" r:id="rId4" display="WebServerInitializedEvent" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/context/WebServerInitializedEvent.html"/>
+    <hyperlink ref="A10" r:id="rId5" display="WebServerPortFileWriter" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/context/WebServerPortFileWriter.html"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
+  <cols>
+    <col min="1" max="1" width="28.8888888888889" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="22.8" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="11" ht="22.8" spans="1:1">
+      <c r="A11" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="ConfigurableJettyWebServerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/jetty/ConfigurableJettyWebServerFactory.html"/>
+    <hyperlink ref="A4" r:id="rId2" display="JettyServerCustomizer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/jetty/JettyServerCustomizer.html"/>
+    <hyperlink ref="A8" r:id="rId3" display="JettyReactiveWebServerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/jetty/JettyReactiveWebServerFactory.html"/>
+    <hyperlink ref="A9" r:id="rId4" display="JettyServletWebServerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/jetty/JettyServletWebServerFactory.html"/>
+    <hyperlink ref="A10" r:id="rId5" display="JettyWebServer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/jetty/JettyWebServer.html"/>
+    <hyperlink ref="A11" r:id="rId6" display="ServletContextInitializerConfiguration" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/jetty/ServletContextInitializerConfiguration.html"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
+  <cols>
+    <col min="1" max="1" width="31.2222222222222" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="NettyRouteProvider" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/netty/NettyRouteProvider.html"/>
+    <hyperlink ref="A4" r:id="rId2" display="NettyServerCustomizer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/netty/NettyServerCustomizer.html"/>
+    <hyperlink ref="A8" r:id="rId3" display="NettyReactiveWebServerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/netty/NettyReactiveWebServerFactory.html"/>
+    <hyperlink ref="A9" r:id="rId4" display="NettyWebServer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/netty/NettyWebServer.html"/>
+    <hyperlink ref="A10" r:id="rId5" display="SslServerCustomizer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/netty/SslServerCustomizer.html"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="37.8888888888889" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="ConfigurableTomcatWebServerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/tomcat/ConfigurableTomcatWebServerFactory.html"/>
+    <hyperlink ref="A4" r:id="rId2" display="TomcatConnectorCustomizer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/tomcat/TomcatConnectorCustomizer.html"/>
+    <hyperlink ref="A5" r:id="rId3" display="TomcatContextCustomizer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/tomcat/TomcatContextCustomizer.html"/>
+    <hyperlink ref="A6" r:id="rId4" display="TomcatProtocolHandlerCustomizer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/tomcat/TomcatProtocolHandlerCustomizer.html"/>
+    <hyperlink ref="A10" r:id="rId5" display="TomcatEmbeddedWebappClassLoader" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/tomcat/TomcatEmbeddedWebappClassLoader.html"/>
+    <hyperlink ref="A11" r:id="rId6" display="TomcatReactiveWebServerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/tomcat/TomcatReactiveWebServerFactory.html"/>
+    <hyperlink ref="A12" r:id="rId7" display="TomcatServletWebServerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/tomcat/TomcatServletWebServerFactory.html"/>
+    <hyperlink ref="A13" r:id="rId8" display="TomcatWebServer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/tomcat/TomcatWebServer.html"/>
+    <hyperlink ref="A17" r:id="rId9" display="ConnectorStartFailedException" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/tomcat/ConnectorStartFailedException.html"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3854,9 +4320,73 @@
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="41.4444444444444" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="ConfigurableUndertowWebServerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/undertow/ConfigurableUndertowWebServerFactory.html"/>
+    <hyperlink ref="A4" r:id="rId2" display="HttpHandlerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/undertow/HttpHandlerFactory.html"/>
+    <hyperlink ref="A5" r:id="rId3" display="UndertowBuilderCustomizer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/undertow/UndertowBuilderCustomizer.html"/>
+    <hyperlink ref="A6" r:id="rId4" display="UndertowDeploymentInfoCustomizer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/undertow/UndertowDeploymentInfoCustomizer.html"/>
+    <hyperlink ref="A10" r:id="rId5" display="UndertowReactiveWebServerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/undertow/UndertowReactiveWebServerFactory.html"/>
+    <hyperlink ref="A11" r:id="rId6" display="UndertowServletWebServer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/undertow/UndertowServletWebServer.html"/>
+    <hyperlink ref="A12" r:id="rId7" display="UndertowServletWebServerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/undertow/UndertowServletWebServerFactory.html"/>
+    <hyperlink ref="A13" r:id="rId8" display="UndertowWebServer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/embedded/undertow/UndertowWebServer.html"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3865,42 +4395,214 @@
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="ErrorAttributes" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/error/ErrorAttributes.html"/>
+    <hyperlink ref="A4" r:id="rId2" display="ErrorWebExceptionHandler" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/error/ErrorWebExceptionHandler.html"/>
+    <hyperlink ref="A8" r:id="rId3" display="DefaultErrorAttributes" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/error/DefaultErrorAttributes.html"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
+  <cols>
+    <col min="1" max="1" width="42.8888888888889" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="ConfigurableReactiveWebApplicationContext" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/context/ConfigurableReactiveWebApplicationContext.html"/>
+    <hyperlink ref="A4" r:id="rId2" display="ConfigurableReactiveWebEnvironment" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/context/ConfigurableReactiveWebEnvironment.html"/>
+    <hyperlink ref="A5" r:id="rId3" display="ReactiveWebApplicationContext" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/context/ReactiveWebApplicationContext.html"/>
+    <hyperlink ref="A9" r:id="rId4" display="AnnotationConfigReactiveWebApplicationContext" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/context/AnnotationConfigReactiveWebApplicationContext.html"/>
+    <hyperlink ref="A10" r:id="rId5" display="AnnotationConfigReactiveWebServerApplicationContext" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/context/AnnotationConfigReactiveWebServerApplicationContext.html"/>
+    <hyperlink ref="A11" r:id="rId6" display="GenericReactiveWebApplicationContext" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/context/GenericReactiveWebApplicationContext.html"/>
+    <hyperlink ref="A12" r:id="rId7" display="ReactiveWebServerApplicationContext" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/context/ReactiveWebServerApplicationContext.html"/>
+    <hyperlink ref="A13" r:id="rId8" display="ReactiveWebServerInitializedEvent" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/context/ReactiveWebServerInitializedEvent.html"/>
+    <hyperlink ref="A14" r:id="rId9" display="StandardReactiveWebEnvironment" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/context/StandardReactiveWebEnvironment.html"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="50.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="ErrorAttributes" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/error/ErrorAttributes.html"/>
+    <hyperlink ref="A4" r:id="rId2" display="ErrorWebExceptionHandler" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/error/ErrorWebExceptionHandler.html"/>
+    <hyperlink ref="A8" r:id="rId3" display="DefaultErrorAttributes" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/error/DefaultErrorAttributes.html"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="37.4444444444444" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1" display="org.springframework.boot.web.reactive.filter" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/filter/package-summary.html"/>
+    <hyperlink ref="A5" r:id="rId2" display="OrderedWebFilter" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/filter/OrderedWebFilter.html"/>
+    <hyperlink ref="A9" r:id="rId3" display="OrderedHiddenHttpMethodFilter" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/filter/OrderedHiddenHttpMethodFilter.html"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3909,9 +4611,26 @@
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2"/>
+  <cols>
+    <col min="1" max="1" width="31.1111111111111" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="WebClientCustomizer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/function/client/WebClientCustomizer.html"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3920,9 +4639,32 @@
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="38.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="MustacheView" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/result/view/MustacheView.html"/>
+    <hyperlink ref="A4" r:id="rId2" display="MustacheViewResolver" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/result/view/MustacheViewResolver.html"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3931,9 +4673,43 @@
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="44.2222222222222" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="ConfigurableReactiveWebServerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/server/ConfigurableReactiveWebServerFactory.html"/>
+    <hyperlink ref="A4" r:id="rId2" display="ReactiveWebServerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/server/ReactiveWebServerFactory.html"/>
+    <hyperlink ref="A8" r:id="rId3" display="AbstractReactiveWebServerFactory" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/web/reactive/server/AbstractReactiveWebServerFactory.html"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3955,42 +4731,42 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>212</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>213</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>215</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>216</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>217</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>218</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>219</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -4000,52 +4776,52 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>220</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>221</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>222</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>223</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>224</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>225</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>226</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>227</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>228</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>229</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -4055,17 +4831,17 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>230</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>231</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>232</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -4075,12 +4851,12 @@
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>233</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -4090,7 +4866,7 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -4115,12 +4891,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>236</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>237</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -4130,47 +4906,47 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>239</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>240</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>241</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>242</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>243</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>244</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>245</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>246</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -4180,7 +4956,7 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>247</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -4190,7 +4966,7 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>248</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -4242,37 +5018,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>253</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>254</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>255</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -4294,12 +5070,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -4309,7 +5085,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -4334,7 +5110,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>259</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -4344,27 +5120,27 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>260</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>261</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>262</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>264</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -4389,12 +5165,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>265</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>266</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -4404,27 +5180,27 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>267</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>268</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>269</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>270</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>271</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -4434,12 +5210,12 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>272</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>273</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -4464,17 +5240,17 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>275</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>276</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -4496,12 +5272,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -4523,12 +5299,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
